--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c771313384576c48/Desktop/new_git/python-minor-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BFA712A-AEA7-4F89-B31F-A19E06AC3F05}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8D491F8-6293-4876-8F16-F65AD4F31EE7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -486,6 +486,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2379,19 +2383,25 @@
         <v>46280</v>
       </c>
       <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
+      <c r="C63" s="14">
+        <v>60</v>
+      </c>
+      <c r="D63" s="14">
+        <v>120</v>
+      </c>
+      <c r="E63" s="14">
+        <v>60</v>
+      </c>
       <c r="F63" s="14"/>
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>240</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="K63" s="16"/>
       <c r="L63" s="16"/>
